--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0024.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0024.xlsx
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Info Overview</t>
+          <t>Tổng Quan Thông Tin</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Outline</t>
+          <t>Đường Viền</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Quit khỏi thử thách hiện tại</t>
+          <t>Thoát khỏi thử thách hiện tại</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Kết thúc và hoàn tất</t>
+          <t>Kết thúc và Xác nhận</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Rời Đi Tạm Thời</t>
+          <t>Tạm rời đi đã</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Investigation Result</t>
+          <t>Kết quả Điều tra</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>Ẩn Dụ</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Thought Evolution</t>
+          <t>Tiến Hóa Tư Duy</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Effect Overview</t>
+          <t>Tổng quan hiệu ứng</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Cấp Độ Tiếp Theo</t>
+          <t>Cấp độ tiếp theo</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Thought Evolution</t>
+          <t>Tiến Hóa Tư Duy</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Điều tra Dị thường</t>
+          <t>Điều tra dị thường</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Điều tra Dị thường</t>
+          <t>Điều tra dị thường</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Metaphor Dictionary</t>
+          <t>Từ Điển Ẩn Dụ</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Total Payment</t>
+          <t>Tổng Thanh Toán</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Trao đổi</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Chọn Metaphor</t>
+          <t>Chọn Ẩn Dụ</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Thời Gian Challenge</t>
+          <t>Thời Gian Thử Thách</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Làm mới</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Tải Lên Nhật Ký</t>
+          <t>Tải Nhật ký lên</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Không Mail to claim</t>
+          <t>Không có thư nào để nhận</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Insufficient Currency for Exchange</t>
+          <t>Tiền tệ không đủ để trao đổi</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Chưa hoàn thành</t>
+          <t>Chưa Hoàn Tất</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Hologram Chiến Thuật</t>
+          <t>Bản Hologram Chiến Thuật</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Ghi Chép</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Retry Challenge</t>
+          <t>Thử lại Thử thách</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Đã thất bại</t>
+          <t>Đã đánh bại</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Chức năng Data Modify mở khóa ở Cấp 21 Data Bank</t>
+          <t>Chức năng Điều Chỉnh Dữ Liệu mở khóa ở Cấp 21 Kho Dữ Liệu</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Chỉ có thể Data Modify trên Echoes 5 sao chưa nâng cấp</t>
+          <t>Chỉ có thể Điều Chỉnh Dữ Liệu trên Echo 5 sao chưa nâng cấp</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Stage Cleared</t>
+          <t>Hoàn Thành Giai Đoạn</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Stage Cleared (Full Combo)</t>
+          <t>Hoàn Thành (Full Combo)</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Stage Cleared (Tất cả Perfect)</t>
+          <t>Hoàn Thành Xuất Sắc (Toàn Perfect)</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Xác nhận và Tiến hành Data Merge</t>
+          <t>Xác nhận và Tiến hành Hợp Nhất Dữ Liệu</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
